--- a/examples/qpt_reports/qpt_demo_report_cnot.xlsx
+++ b/examples/qpt_reports/qpt_demo_report_cnot.xlsx
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>0.1675044874430627</v>
+        <v>0.1665954236674892</v>
       </c>
       <c r="C11" s="4" t="n"/>
       <c r="D11" s="4" t="n"/>
@@ -737,10 +737,10 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>4031</v>
+        <v>4053</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>4065</v>
+        <v>4043</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>0</v>
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>4018</v>
+        <v>4031</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>4078</v>
+        <v>4065</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0</v>
@@ -794,13 +794,13 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>4084</v>
+        <v>4029</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>4012</v>
+        <v>4067</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>0</v>
@@ -813,16 +813,16 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2054</v>
+        <v>2021</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2012</v>
+        <v>1985</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2021</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="8">
@@ -832,16 +832,16 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>2081</v>
+        <v>2053</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1944</v>
+        <v>2023</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>2000</v>
+        <v>2055</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2071</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="9">
@@ -851,13 +851,13 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>4121</v>
+        <v>4071</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>3975</v>
+        <v>4025</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>0</v>
@@ -870,13 +870,13 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>4099</v>
+        <v>4017</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3997</v>
+        <v>4079</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>0</v>
@@ -889,16 +889,16 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>1990</v>
+        <v>1988</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1993</v>
+        <v>1995</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2060</v>
+        <v>2049</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2053</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="12">
@@ -908,16 +908,16 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>1951</v>
+        <v>2020</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2022</v>
+        <v>2060</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>2092</v>
+        <v>2006</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2031</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="13">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>4113</v>
+        <v>4038</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>3983</v>
+        <v>4058</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>0</v>
@@ -965,10 +965,10 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>4014</v>
+        <v>4060</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>4082</v>
+        <v>4036</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>0</v>
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>3992</v>
+        <v>4083</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>4104</v>
+        <v>4013</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>0</v>
@@ -1022,10 +1022,10 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>4141</v>
+        <v>4117</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>3955</v>
+        <v>3979</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>0</v>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>4043</v>
+        <v>3956</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>4053</v>
+        <v>4140</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>0</v>
@@ -1079,10 +1079,10 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>4048</v>
+        <v>4008</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>4048</v>
+        <v>4088</v>
       </c>
       <c r="D21" s="4" t="n">
         <v>0</v>
@@ -1098,16 +1098,16 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>2032</v>
+        <v>2011</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2033</v>
+        <v>2005</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2027</v>
+        <v>2058</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2004</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="23">
@@ -1117,13 +1117,13 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>4035</v>
+        <v>4070</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>4061</v>
+        <v>4026</v>
       </c>
       <c r="E23" s="4" t="n">
         <v>0</v>
@@ -1136,16 +1136,16 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>2033</v>
+        <v>2072</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2042</v>
+        <v>2064</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2005</v>
+        <v>1998</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2016</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="25">
@@ -1155,16 +1155,16 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>1953</v>
+        <v>1996</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1999</v>
+        <v>2060</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2068</v>
+        <v>2018</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2076</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="26">
@@ -1174,16 +1174,16 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2043</v>
+        <v>2038</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>2026</v>
+        <v>1982</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2015</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="27">
@@ -1193,13 +1193,13 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>4094</v>
+        <v>4118</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>4002</v>
+        <v>3978</v>
       </c>
       <c r="E27" s="4" t="n">
         <v>0</v>
@@ -1212,16 +1212,16 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>2051</v>
+        <v>2113</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2036</v>
+        <v>1977</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>2096</v>
+        <v>2000</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1913</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="29">
@@ -1231,16 +1231,16 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>2024</v>
+        <v>2095</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2069</v>
+        <v>1958</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>2046</v>
+        <v>1953</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1957</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="30">
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>4049</v>
+        <v>4043</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>4047</v>
+        <v>4053</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>0</v>
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>3919</v>
+        <v>4155</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>4177</v>
+        <v>3941</v>
       </c>
       <c r="D32" s="4" t="n">
         <v>0</v>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>4029</v>
+        <v>4082</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>4067</v>
+        <v>4014</v>
       </c>
       <c r="D33" s="4" t="n">
         <v>0</v>
@@ -1326,10 +1326,10 @@
         </is>
       </c>
       <c r="B34" s="4" t="n">
-        <v>4061</v>
+        <v>3988</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>4035</v>
+        <v>4108</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>0</v>
@@ -1345,10 +1345,10 @@
         </is>
       </c>
       <c r="B35" s="4" t="n">
-        <v>3973</v>
+        <v>4128</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>4123</v>
+        <v>3968</v>
       </c>
       <c r="D35" s="4" t="n">
         <v>0</v>
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="B37" s="4" t="n">
-        <v>4134</v>
+        <v>4060</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>3962</v>
+        <v>4036</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>0</v>
@@ -1402,16 +1402,16 @@
         </is>
       </c>
       <c r="B38" s="4" t="n">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="C38" s="4" t="n">
-        <v>2039</v>
+        <v>2062</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>2037</v>
+        <v>2028</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>2029</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="39">
@@ -1421,16 +1421,16 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>2044</v>
+        <v>1967</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>2050</v>
+        <v>2082</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>1997</v>
+        <v>1979</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>2005</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="40">
@@ -1440,13 +1440,13 @@
         </is>
       </c>
       <c r="B40" s="4" t="n">
-        <v>4026</v>
+        <v>4112</v>
       </c>
       <c r="C40" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>4070</v>
+        <v>3984</v>
       </c>
       <c r="E40" s="4" t="n">
         <v>0</v>
@@ -1459,16 +1459,16 @@
         </is>
       </c>
       <c r="B41" s="4" t="n">
-        <v>2047</v>
+        <v>1987</v>
       </c>
       <c r="C41" s="4" t="n">
-        <v>1942</v>
+        <v>2019</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>2043</v>
+        <v>2035</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>2064</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="42">
@@ -1478,16 +1478,16 @@
         </is>
       </c>
       <c r="B42" s="4" t="n">
+        <v>1996</v>
+      </c>
+      <c r="C42" s="4" t="n">
         <v>2002</v>
       </c>
-      <c r="C42" s="4" t="n">
-        <v>2064</v>
-      </c>
       <c r="D42" s="4" t="n">
-        <v>2029</v>
+        <v>2044</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>2001</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="43">
@@ -1497,16 +1497,16 @@
         </is>
       </c>
       <c r="B43" s="4" t="n">
-        <v>2051</v>
+        <v>2043</v>
       </c>
       <c r="C43" s="4" t="n">
-        <v>2002</v>
+        <v>1968</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>2026</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="44">
@@ -1516,13 +1516,13 @@
         </is>
       </c>
       <c r="B44" s="4" t="n">
-        <v>4063</v>
+        <v>4053</v>
       </c>
       <c r="C44" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>4033</v>
+        <v>4043</v>
       </c>
       <c r="E44" s="4" t="n">
         <v>0</v>
@@ -1535,16 +1535,16 @@
         </is>
       </c>
       <c r="B45" s="4" t="n">
-        <v>1989</v>
+        <v>2068</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>1966</v>
+        <v>1907</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>2082</v>
+        <v>2064</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>2059</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="46">
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="B46" s="4" t="n">
-        <v>4086</v>
+        <v>4075</v>
       </c>
       <c r="C46" s="4" t="n">
-        <v>4010</v>
+        <v>4021</v>
       </c>
       <c r="D46" s="4" t="n">
         <v>0</v>
@@ -1573,10 +1573,10 @@
         </is>
       </c>
       <c r="B47" s="4" t="n">
-        <v>4084</v>
+        <v>4021</v>
       </c>
       <c r="C47" s="4" t="n">
-        <v>4012</v>
+        <v>4075</v>
       </c>
       <c r="D47" s="4" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="B49" s="4" t="n">
-        <v>4045</v>
+        <v>4057</v>
       </c>
       <c r="C49" s="4" t="n">
-        <v>4051</v>
+        <v>4039</v>
       </c>
       <c r="D49" s="4" t="n">
         <v>0</v>
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="B51" s="4" t="n">
-        <v>4128</v>
+        <v>4076</v>
       </c>
       <c r="C51" s="4" t="n">
-        <v>3968</v>
+        <v>4020</v>
       </c>
       <c r="D51" s="4" t="n">
         <v>0</v>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="B52" s="4" t="n">
-        <v>4070</v>
+        <v>4027</v>
       </c>
       <c r="C52" s="4" t="n">
-        <v>4026</v>
+        <v>4069</v>
       </c>
       <c r="D52" s="4" t="n">
         <v>0</v>
@@ -1706,13 +1706,13 @@
         </is>
       </c>
       <c r="B54" s="4" t="n">
-        <v>3994</v>
+        <v>4080</v>
       </c>
       <c r="C54" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>4102</v>
+        <v>4016</v>
       </c>
       <c r="E54" s="4" t="n">
         <v>0</v>
@@ -1725,16 +1725,16 @@
         </is>
       </c>
       <c r="B55" s="4" t="n">
-        <v>1976</v>
+        <v>2027</v>
       </c>
       <c r="C55" s="4" t="n">
-        <v>2073</v>
+        <v>2018</v>
       </c>
       <c r="D55" s="4" t="n">
         <v>2047</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>2000</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="56">
@@ -1744,16 +1744,16 @@
         </is>
       </c>
       <c r="B56" s="4" t="n">
-        <v>2050</v>
+        <v>2000</v>
       </c>
       <c r="C56" s="4" t="n">
-        <v>1972</v>
+        <v>2053</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>2036</v>
+        <v>1947</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>2038</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="57">
@@ -1763,13 +1763,13 @@
         </is>
       </c>
       <c r="B57" s="4" t="n">
-        <v>4113</v>
+        <v>4002</v>
       </c>
       <c r="C57" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>3983</v>
+        <v>4094</v>
       </c>
       <c r="E57" s="4" t="n">
         <v>0</v>
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B58" s="4" t="n">
-        <v>4021</v>
+        <v>4124</v>
       </c>
       <c r="C58" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>4075</v>
+        <v>3972</v>
       </c>
       <c r="E58" s="4" t="n">
         <v>0</v>
@@ -1801,16 +1801,16 @@
         </is>
       </c>
       <c r="B59" s="4" t="n">
-        <v>1978</v>
+        <v>1990</v>
       </c>
       <c r="C59" s="4" t="n">
-        <v>1991</v>
+        <v>2008</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>2082</v>
+        <v>1995</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>2045</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="60">
@@ -1820,16 +1820,16 @@
         </is>
       </c>
       <c r="B60" s="4" t="n">
-        <v>2024</v>
+        <v>2012</v>
       </c>
       <c r="C60" s="4" t="n">
-        <v>2029</v>
+        <v>2033</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>2016</v>
+        <v>1947</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>2027</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="61">
@@ -1839,13 +1839,13 @@
         </is>
       </c>
       <c r="B61" s="4" t="n">
-        <v>4068</v>
+        <v>4078</v>
       </c>
       <c r="C61" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>4028</v>
+        <v>4018</v>
       </c>
       <c r="E61" s="4" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="B63" s="4" t="n">
-        <v>4017</v>
+        <v>4058</v>
       </c>
       <c r="C63" s="4" t="n">
-        <v>4079</v>
+        <v>4038</v>
       </c>
       <c r="D63" s="4" t="n">
         <v>0</v>
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="B64" s="4" t="n">
-        <v>3926</v>
+        <v>4042</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>4170</v>
+        <v>4054</v>
       </c>
       <c r="D64" s="4" t="n">
         <v>0</v>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="B66" s="4" t="n">
-        <v>4086</v>
+        <v>4011</v>
       </c>
       <c r="C66" s="4" t="n">
         <v>0</v>
@@ -1943,7 +1943,7 @@
         <v>0</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>4010</v>
+        <v>4085</v>
       </c>
     </row>
     <row r="67">
@@ -1953,16 +1953,16 @@
         </is>
       </c>
       <c r="B67" s="4" t="n">
-        <v>1981</v>
+        <v>2024</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>2102</v>
+        <v>2021</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>1969</v>
+        <v>2035</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>2044</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="68">
@@ -1972,16 +1972,16 @@
         </is>
       </c>
       <c r="B68" s="4" t="n">
-        <v>2061</v>
+        <v>2043</v>
       </c>
       <c r="C68" s="4" t="n">
-        <v>2028</v>
+        <v>2058</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>2025</v>
+        <v>2005</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>1982</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="69">
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="B69" s="4" t="n">
-        <v>4049</v>
+        <v>4034</v>
       </c>
       <c r="C69" s="4" t="n">
         <v>0</v>
@@ -2000,7 +2000,7 @@
         <v>0</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>4047</v>
+        <v>4062</v>
       </c>
     </row>
     <row r="70">
@@ -2010,16 +2010,16 @@
         </is>
       </c>
       <c r="B70" s="4" t="n">
-        <v>2001</v>
+        <v>1963</v>
       </c>
       <c r="C70" s="4" t="n">
-        <v>2056</v>
+        <v>2047</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>2026</v>
+        <v>2087</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>2013</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="71">
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="B71" s="4" t="n">
-        <v>4028</v>
+        <v>4067</v>
       </c>
       <c r="C71" s="4" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>4068</v>
+        <v>4029</v>
       </c>
     </row>
     <row r="72">
@@ -2048,16 +2048,16 @@
         </is>
       </c>
       <c r="B72" s="4" t="n">
-        <v>1998</v>
+        <v>2048</v>
       </c>
       <c r="C72" s="4" t="n">
-        <v>2049</v>
+        <v>2003</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>2061</v>
+        <v>2035</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>1988</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="73">
@@ -2067,16 +2067,16 @@
         </is>
       </c>
       <c r="B73" s="4" t="n">
-        <v>2038</v>
+        <v>1997</v>
       </c>
       <c r="C73" s="4" t="n">
-        <v>2077</v>
+        <v>2029</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>1992</v>
+        <v>2056</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>1989</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="74">
@@ -2086,16 +2086,16 @@
         </is>
       </c>
       <c r="B74" s="4" t="n">
-        <v>2025</v>
+        <v>2030</v>
       </c>
       <c r="C74" s="4" t="n">
-        <v>2040</v>
+        <v>2052</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>2022</v>
+        <v>1950</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>2009</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="75">
@@ -2105,16 +2105,16 @@
         </is>
       </c>
       <c r="B75" s="4" t="n">
-        <v>2008</v>
+        <v>2036</v>
       </c>
       <c r="C75" s="4" t="n">
-        <v>2002</v>
+        <v>2033</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>2035</v>
+        <v>2049</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>2051</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="76">
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="C76" s="4" t="n">
-        <v>4008</v>
+        <v>4065</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>4088</v>
+        <v>4031</v>
       </c>
       <c r="E76" s="4" t="n">
         <v>0</v>
@@ -2143,16 +2143,16 @@
         </is>
       </c>
       <c r="B77" s="4" t="n">
-        <v>1997</v>
+        <v>2009</v>
       </c>
       <c r="C77" s="4" t="n">
-        <v>2044</v>
+        <v>2063</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>2001</v>
+        <v>1962</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>2054</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="78">
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="B78" s="4" t="n">
-        <v>4056</v>
+        <v>4055</v>
       </c>
       <c r="C78" s="4" t="n">
         <v>0</v>
@@ -2171,7 +2171,7 @@
         <v>0</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>4040</v>
+        <v>4041</v>
       </c>
     </row>
     <row r="79">
@@ -2181,16 +2181,16 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>1991</v>
+        <v>2081</v>
       </c>
       <c r="C79" s="4" t="n">
-        <v>2067</v>
+        <v>2055</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>2039</v>
+        <v>1949</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>1999</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="80">
@@ -2200,16 +2200,16 @@
         </is>
       </c>
       <c r="B80" s="4" t="n">
-        <v>2147</v>
+        <v>1998</v>
       </c>
       <c r="C80" s="4" t="n">
-        <v>1959</v>
+        <v>2019</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>1986</v>
+        <v>2038</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>2004</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="81">
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="B81" s="4" t="n">
-        <v>4116</v>
+        <v>3992</v>
       </c>
       <c r="C81" s="4" t="n">
         <v>0</v>
@@ -2228,7 +2228,7 @@
         <v>0</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>3980</v>
+        <v>4104</v>
       </c>
     </row>
     <row r="82">
@@ -2238,16 +2238,16 @@
         </is>
       </c>
       <c r="B82" s="4" t="n">
-        <v>2051</v>
+        <v>2078</v>
       </c>
       <c r="C82" s="4" t="n">
-        <v>2072</v>
+        <v>2034</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>1935</v>
+        <v>2003</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>2038</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="83">
@@ -2257,13 +2257,13 @@
         </is>
       </c>
       <c r="B83" s="4" t="n">
-        <v>3981</v>
+        <v>3953</v>
       </c>
       <c r="C83" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>4115</v>
+        <v>4143</v>
       </c>
       <c r="E83" s="4" t="n">
         <v>0</v>
@@ -2276,16 +2276,16 @@
         </is>
       </c>
       <c r="B84" s="4" t="n">
-        <v>2021</v>
+        <v>1986</v>
       </c>
       <c r="C84" s="4" t="n">
-        <v>2079</v>
+        <v>2023</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>1961</v>
+        <v>1999</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>2035</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="85">
@@ -2295,16 +2295,16 @@
         </is>
       </c>
       <c r="B85" s="4" t="n">
-        <v>1973</v>
+        <v>1959</v>
       </c>
       <c r="C85" s="4" t="n">
-        <v>2043</v>
+        <v>2057</v>
       </c>
       <c r="D85" s="4" t="n">
-        <v>2012</v>
+        <v>2050</v>
       </c>
       <c r="E85" s="4" t="n">
-        <v>2068</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="86">
@@ -2314,10 +2314,10 @@
         </is>
       </c>
       <c r="B86" s="4" t="n">
-        <v>4019</v>
+        <v>3980</v>
       </c>
       <c r="C86" s="4" t="n">
-        <v>4077</v>
+        <v>4116</v>
       </c>
       <c r="D86" s="4" t="n">
         <v>0</v>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="B88" s="4" t="n">
-        <v>4060</v>
+        <v>4058</v>
       </c>
       <c r="C88" s="4" t="n">
-        <v>4036</v>
+        <v>4038</v>
       </c>
       <c r="D88" s="4" t="n">
         <v>0</v>
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="B89" s="4" t="n">
-        <v>4030</v>
+        <v>4021</v>
       </c>
       <c r="C89" s="4" t="n">
-        <v>4066</v>
+        <v>4075</v>
       </c>
       <c r="D89" s="4" t="n">
         <v>0</v>
@@ -2390,16 +2390,16 @@
         </is>
       </c>
       <c r="B90" s="4" t="n">
-        <v>1989</v>
+        <v>2086</v>
       </c>
       <c r="C90" s="4" t="n">
-        <v>2025</v>
+        <v>1987</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>2098</v>
+        <v>2073</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>1984</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="91">
@@ -2409,13 +2409,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>4088</v>
+        <v>4116</v>
       </c>
       <c r="C91" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>4008</v>
+        <v>3980</v>
       </c>
       <c r="E91" s="4" t="n">
         <v>0</v>
@@ -2428,16 +2428,16 @@
         </is>
       </c>
       <c r="B92" s="4" t="n">
-        <v>2109</v>
+        <v>1983</v>
       </c>
       <c r="C92" s="4" t="n">
-        <v>2051</v>
+        <v>1990</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>1975</v>
+        <v>2035</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>1961</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="93">
@@ -2447,16 +2447,16 @@
         </is>
       </c>
       <c r="B93" s="4" t="n">
-        <v>2040</v>
+        <v>2026</v>
       </c>
       <c r="C93" s="4" t="n">
-        <v>2020</v>
+        <v>1962</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>2021</v>
+        <v>2074</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>2015</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="94">
@@ -2466,16 +2466,16 @@
         </is>
       </c>
       <c r="B94" s="4" t="n">
-        <v>2054</v>
+        <v>2005</v>
       </c>
       <c r="C94" s="4" t="n">
-        <v>1927</v>
+        <v>1931</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>2068</v>
+        <v>2116</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>2047</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="95">
@@ -2485,13 +2485,13 @@
         </is>
       </c>
       <c r="B95" s="4" t="n">
-        <v>3994</v>
+        <v>4044</v>
       </c>
       <c r="C95" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>4102</v>
+        <v>4052</v>
       </c>
       <c r="E95" s="4" t="n">
         <v>0</v>
@@ -2504,16 +2504,16 @@
         </is>
       </c>
       <c r="B96" s="4" t="n">
-        <v>1974</v>
+        <v>1938</v>
       </c>
       <c r="C96" s="4" t="n">
-        <v>2055</v>
+        <v>1964</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>2043</v>
+        <v>2086</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>2024</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="97">
@@ -2523,16 +2523,16 @@
         </is>
       </c>
       <c r="B97" s="4" t="n">
-        <v>2042</v>
+        <v>2067</v>
       </c>
       <c r="C97" s="4" t="n">
-        <v>1985</v>
+        <v>1980</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>2065</v>
+        <v>2062</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>2004</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="98">
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="B98" s="4" t="n">
-        <v>1982</v>
+        <v>2023</v>
       </c>
       <c r="C98" s="4" t="n">
-        <v>2004</v>
+        <v>2033</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>2048</v>
+        <v>1990</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>2062</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="99">
@@ -2561,16 +2561,16 @@
         </is>
       </c>
       <c r="B99" s="4" t="n">
-        <v>2012</v>
+        <v>2082</v>
       </c>
       <c r="C99" s="4" t="n">
-        <v>2006</v>
+        <v>1989</v>
       </c>
       <c r="D99" s="4" t="n">
-        <v>2070</v>
+        <v>2031</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>2008</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="100">
@@ -2580,7 +2580,7 @@
         </is>
       </c>
       <c r="B100" s="4" t="n">
-        <v>4137</v>
+        <v>4046</v>
       </c>
       <c r="C100" s="4" t="n">
         <v>0</v>
@@ -2589,7 +2589,7 @@
         <v>0</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>3959</v>
+        <v>4050</v>
       </c>
     </row>
     <row r="101">
@@ -2599,16 +2599,16 @@
         </is>
       </c>
       <c r="B101" s="4" t="n">
-        <v>2044</v>
+        <v>2050</v>
       </c>
       <c r="C101" s="4" t="n">
-        <v>2103</v>
+        <v>2025</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>1989</v>
+        <v>2031</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>1960</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="102">
@@ -2618,16 +2618,16 @@
         </is>
       </c>
       <c r="B102" s="4" t="n">
-        <v>1975</v>
+        <v>2037</v>
       </c>
       <c r="C102" s="4" t="n">
-        <v>2085</v>
+        <v>2017</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>2017</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="103">
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="B103" s="4" t="n">
-        <v>4123</v>
+        <v>4099</v>
       </c>
       <c r="C103" s="4" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
         <v>0</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>3973</v>
+        <v>3997</v>
       </c>
     </row>
     <row r="104">
@@ -2656,16 +2656,16 @@
         </is>
       </c>
       <c r="B104" s="4" t="n">
-        <v>1958</v>
+        <v>2050</v>
       </c>
       <c r="C104" s="4" t="n">
-        <v>2030</v>
+        <v>2022</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>2069</v>
+        <v>1952</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>2039</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="105">
@@ -2675,16 +2675,16 @@
         </is>
       </c>
       <c r="B105" s="4" t="n">
-        <v>1984</v>
+        <v>2012</v>
       </c>
       <c r="C105" s="4" t="n">
-        <v>2061</v>
+        <v>1999</v>
       </c>
       <c r="D105" s="4" t="n">
-        <v>2055</v>
+        <v>2050</v>
       </c>
       <c r="E105" s="4" t="n">
-        <v>1996</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="106">
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="B106" s="4" t="n">
-        <v>4027</v>
+        <v>4092</v>
       </c>
       <c r="C106" s="4" t="n">
         <v>0</v>
@@ -2703,7 +2703,7 @@
         <v>0</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>4069</v>
+        <v>4004</v>
       </c>
     </row>
     <row r="107">
@@ -2713,16 +2713,16 @@
         </is>
       </c>
       <c r="B107" s="4" t="n">
-        <v>2038</v>
+        <v>2035</v>
       </c>
       <c r="C107" s="4" t="n">
-        <v>1985</v>
+        <v>2034</v>
       </c>
       <c r="D107" s="4" t="n">
-        <v>2028</v>
+        <v>2018</v>
       </c>
       <c r="E107" s="4" t="n">
-        <v>2045</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="108">
@@ -2732,16 +2732,16 @@
         </is>
       </c>
       <c r="B108" s="4" t="n">
-        <v>2056</v>
+        <v>2019</v>
       </c>
       <c r="C108" s="4" t="n">
-        <v>2019</v>
+        <v>2047</v>
       </c>
       <c r="D108" s="4" t="n">
-        <v>2006</v>
+        <v>2002</v>
       </c>
       <c r="E108" s="4" t="n">
-        <v>2015</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="109">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="B109" s="4" t="n">
-        <v>4151</v>
+        <v>3950</v>
       </c>
       <c r="C109" s="4" t="n">
         <v>0</v>
@@ -2760,7 +2760,7 @@
         <v>0</v>
       </c>
       <c r="E109" s="4" t="n">
-        <v>3945</v>
+        <v>4146</v>
       </c>
     </row>
     <row r="110">
@@ -2770,16 +2770,16 @@
         </is>
       </c>
       <c r="B110" s="4" t="n">
-        <v>2031</v>
+        <v>2046</v>
       </c>
       <c r="C110" s="4" t="n">
-        <v>1995</v>
+        <v>1990</v>
       </c>
       <c r="D110" s="4" t="n">
-        <v>2039</v>
+        <v>2015</v>
       </c>
       <c r="E110" s="4" t="n">
-        <v>2031</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="111">
@@ -2789,16 +2789,16 @@
         </is>
       </c>
       <c r="B111" s="4" t="n">
-        <v>2023</v>
+        <v>1973</v>
       </c>
       <c r="C111" s="4" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D111" s="4" t="n">
-        <v>2067</v>
+        <v>2060</v>
       </c>
       <c r="E111" s="4" t="n">
-        <v>1983</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="112">
@@ -2808,7 +2808,7 @@
         </is>
       </c>
       <c r="B112" s="4" t="n">
-        <v>4116</v>
+        <v>4053</v>
       </c>
       <c r="C112" s="4" t="n">
         <v>0</v>
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="E112" s="4" t="n">
-        <v>3980</v>
+        <v>4043</v>
       </c>
     </row>
     <row r="113">
@@ -2827,16 +2827,16 @@
         </is>
       </c>
       <c r="B113" s="4" t="n">
-        <v>2020</v>
+        <v>1982</v>
       </c>
       <c r="C113" s="4" t="n">
-        <v>2015</v>
+        <v>1999</v>
       </c>
       <c r="D113" s="4" t="n">
-        <v>2052</v>
+        <v>2070</v>
       </c>
       <c r="E113" s="4" t="n">
-        <v>2009</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="114">
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="B114" s="4" t="n">
-        <v>4056</v>
+        <v>4119</v>
       </c>
       <c r="C114" s="4" t="n">
         <v>0</v>
@@ -2855,7 +2855,7 @@
         <v>0</v>
       </c>
       <c r="E114" s="4" t="n">
-        <v>4040</v>
+        <v>3977</v>
       </c>
     </row>
     <row r="115">
@@ -2865,16 +2865,16 @@
         </is>
       </c>
       <c r="B115" s="4" t="n">
-        <v>2042</v>
+        <v>2049</v>
       </c>
       <c r="C115" s="4" t="n">
-        <v>2012</v>
+        <v>1998</v>
       </c>
       <c r="D115" s="4" t="n">
-        <v>2036</v>
+        <v>2023</v>
       </c>
       <c r="E115" s="4" t="n">
-        <v>2006</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="116">
@@ -2884,16 +2884,16 @@
         </is>
       </c>
       <c r="B116" s="4" t="n">
-        <v>2024</v>
+        <v>2009</v>
       </c>
       <c r="C116" s="4" t="n">
-        <v>1981</v>
+        <v>2019</v>
       </c>
       <c r="D116" s="4" t="n">
-        <v>2082</v>
+        <v>1955</v>
       </c>
       <c r="E116" s="4" t="n">
-        <v>2009</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="117">
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="B117" s="4" t="n">
-        <v>4069</v>
+        <v>4065</v>
       </c>
       <c r="C117" s="4" t="n">
         <v>0</v>
@@ -2912,7 +2912,7 @@
         <v>0</v>
       </c>
       <c r="E117" s="4" t="n">
-        <v>4027</v>
+        <v>4031</v>
       </c>
     </row>
     <row r="118">
@@ -2922,16 +2922,16 @@
         </is>
       </c>
       <c r="B118" s="4" t="n">
-        <v>1923</v>
+        <v>2015</v>
       </c>
       <c r="C118" s="4" t="n">
-        <v>1994</v>
+        <v>2016</v>
       </c>
       <c r="D118" s="4" t="n">
-        <v>2138</v>
+        <v>2054</v>
       </c>
       <c r="E118" s="4" t="n">
-        <v>2041</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="119">
@@ -2941,7 +2941,7 @@
         </is>
       </c>
       <c r="B119" s="4" t="n">
-        <v>4145</v>
+        <v>4052</v>
       </c>
       <c r="C119" s="4" t="n">
         <v>0</v>
@@ -2950,7 +2950,7 @@
         <v>0</v>
       </c>
       <c r="E119" s="4" t="n">
-        <v>3951</v>
+        <v>4044</v>
       </c>
     </row>
     <row r="120">
@@ -2960,16 +2960,16 @@
         </is>
       </c>
       <c r="B120" s="4" t="n">
-        <v>2032</v>
+        <v>1986</v>
       </c>
       <c r="C120" s="4" t="n">
-        <v>1986</v>
+        <v>2026</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>2019</v>
+        <v>2044</v>
       </c>
       <c r="E120" s="4" t="n">
-        <v>2059</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="121">
@@ -2979,16 +2979,16 @@
         </is>
       </c>
       <c r="B121" s="4" t="n">
-        <v>2050</v>
+        <v>2031</v>
       </c>
       <c r="C121" s="4" t="n">
-        <v>2050</v>
+        <v>2017</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>1991</v>
+        <v>2052</v>
       </c>
       <c r="E121" s="4" t="n">
-        <v>2005</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="122">
@@ -2998,16 +2998,16 @@
         </is>
       </c>
       <c r="B122" s="4" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C122" s="4" t="n">
-        <v>2079</v>
+        <v>2023</v>
       </c>
       <c r="D122" s="4" t="n">
-        <v>2016</v>
+        <v>1945</v>
       </c>
       <c r="E122" s="4" t="n">
-        <v>1982</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="123">
@@ -3017,16 +3017,16 @@
         </is>
       </c>
       <c r="B123" s="4" t="n">
-        <v>2058</v>
+        <v>2083</v>
       </c>
       <c r="C123" s="4" t="n">
-        <v>2031</v>
+        <v>1966</v>
       </c>
       <c r="D123" s="4" t="n">
-        <v>1973</v>
+        <v>2097</v>
       </c>
       <c r="E123" s="4" t="n">
-        <v>2034</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="124">
@@ -3039,10 +3039,10 @@
         <v>0</v>
       </c>
       <c r="C124" s="4" t="n">
-        <v>4046</v>
+        <v>4101</v>
       </c>
       <c r="D124" s="4" t="n">
-        <v>4050</v>
+        <v>3995</v>
       </c>
       <c r="E124" s="4" t="n">
         <v>0</v>
@@ -3055,16 +3055,16 @@
         </is>
       </c>
       <c r="B125" s="4" t="n">
-        <v>1997</v>
+        <v>2062</v>
       </c>
       <c r="C125" s="4" t="n">
-        <v>2055</v>
+        <v>1959</v>
       </c>
       <c r="D125" s="4" t="n">
-        <v>2023</v>
+        <v>1977</v>
       </c>
       <c r="E125" s="4" t="n">
-        <v>2021</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="126">
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="B126" s="4" t="n">
-        <v>4036</v>
+        <v>4043</v>
       </c>
       <c r="C126" s="4" t="n">
         <v>0</v>
@@ -3083,7 +3083,7 @@
         <v>0</v>
       </c>
       <c r="E126" s="4" t="n">
-        <v>4060</v>
+        <v>4053</v>
       </c>
     </row>
     <row r="127">
@@ -3093,16 +3093,16 @@
         </is>
       </c>
       <c r="B127" s="4" t="n">
-        <v>1985</v>
+        <v>1983</v>
       </c>
       <c r="C127" s="4" t="n">
-        <v>2075</v>
+        <v>2037</v>
       </c>
       <c r="D127" s="4" t="n">
-        <v>2004</v>
+        <v>1998</v>
       </c>
       <c r="E127" s="4" t="n">
-        <v>2032</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="128">
@@ -3112,16 +3112,16 @@
         </is>
       </c>
       <c r="B128" s="4" t="n">
-        <v>1985</v>
+        <v>2102</v>
       </c>
       <c r="C128" s="4" t="n">
-        <v>1967</v>
+        <v>2014</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>2105</v>
+        <v>2017</v>
       </c>
       <c r="E128" s="4" t="n">
-        <v>2039</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="129">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="B129" s="4" t="n">
-        <v>4110</v>
+        <v>4108</v>
       </c>
       <c r="C129" s="4" t="n">
         <v>0</v>
@@ -3140,7 +3140,7 @@
         <v>0</v>
       </c>
       <c r="E129" s="4" t="n">
-        <v>3986</v>
+        <v>3988</v>
       </c>
     </row>
     <row r="130">
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="B130" s="4" t="n">
-        <v>4110</v>
+        <v>4044</v>
       </c>
       <c r="C130" s="4" t="n">
         <v>0</v>
@@ -3159,7 +3159,7 @@
         <v>0</v>
       </c>
       <c r="E130" s="4" t="n">
-        <v>3986</v>
+        <v>4052</v>
       </c>
     </row>
     <row r="131">
@@ -3169,16 +3169,16 @@
         </is>
       </c>
       <c r="B131" s="4" t="n">
-        <v>1970</v>
+        <v>1987</v>
       </c>
       <c r="C131" s="4" t="n">
-        <v>2054</v>
+        <v>1983</v>
       </c>
       <c r="D131" s="4" t="n">
-        <v>2008</v>
+        <v>2061</v>
       </c>
       <c r="E131" s="4" t="n">
-        <v>2064</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="132">
@@ -3188,16 +3188,16 @@
         </is>
       </c>
       <c r="B132" s="4" t="n">
-        <v>2101</v>
+        <v>2098</v>
       </c>
       <c r="C132" s="4" t="n">
-        <v>2008</v>
+        <v>1991</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>2024</v>
+        <v>1975</v>
       </c>
       <c r="E132" s="4" t="n">
-        <v>1963</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="133">
@@ -3207,7 +3207,7 @@
         </is>
       </c>
       <c r="B133" s="4" t="n">
-        <v>4132</v>
+        <v>4025</v>
       </c>
       <c r="C133" s="4" t="n">
         <v>0</v>
@@ -3216,7 +3216,7 @@
         <v>0</v>
       </c>
       <c r="E133" s="4" t="n">
-        <v>3964</v>
+        <v>4071</v>
       </c>
     </row>
     <row r="134">
@@ -3226,16 +3226,16 @@
         </is>
       </c>
       <c r="B134" s="4" t="n">
-        <v>2045</v>
+        <v>2030</v>
       </c>
       <c r="C134" s="4" t="n">
-        <v>1960</v>
+        <v>2017</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>2092</v>
+        <v>2034</v>
       </c>
       <c r="E134" s="4" t="n">
-        <v>1999</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="135">
@@ -3245,16 +3245,16 @@
         </is>
       </c>
       <c r="B135" s="4" t="n">
-        <v>2049</v>
+        <v>2038</v>
       </c>
       <c r="C135" s="4" t="n">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="D135" s="4" t="n">
-        <v>2027</v>
+        <v>1979</v>
       </c>
       <c r="E135" s="4" t="n">
-        <v>2005</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="136">
@@ -3264,7 +3264,7 @@
         </is>
       </c>
       <c r="B136" s="4" t="n">
-        <v>4091</v>
+        <v>4070</v>
       </c>
       <c r="C136" s="4" t="n">
         <v>0</v>
@@ -3273,7 +3273,7 @@
         <v>0</v>
       </c>
       <c r="E136" s="4" t="n">
-        <v>4005</v>
+        <v>4026</v>
       </c>
     </row>
     <row r="137">
@@ -3283,16 +3283,16 @@
         </is>
       </c>
       <c r="B137" s="4" t="n">
-        <v>1977</v>
+        <v>2017</v>
       </c>
       <c r="C137" s="4" t="n">
-        <v>2039</v>
+        <v>1975</v>
       </c>
       <c r="D137" s="4" t="n">
-        <v>2071</v>
+        <v>2093</v>
       </c>
       <c r="E137" s="4" t="n">
-        <v>2009</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="138">
@@ -3302,16 +3302,16 @@
         </is>
       </c>
       <c r="B138" s="4" t="n">
-        <v>2036</v>
+        <v>1973</v>
       </c>
       <c r="C138" s="4" t="n">
+        <v>2075</v>
+      </c>
+      <c r="D138" s="4" t="n">
+        <v>2089</v>
+      </c>
+      <c r="E138" s="4" t="n">
         <v>1959</v>
-      </c>
-      <c r="D138" s="4" t="n">
-        <v>2100</v>
-      </c>
-      <c r="E138" s="4" t="n">
-        <v>2001</v>
       </c>
     </row>
     <row r="139">
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="B139" s="4" t="n">
-        <v>4094</v>
+        <v>4047</v>
       </c>
       <c r="C139" s="4" t="n">
         <v>0</v>
@@ -3330,7 +3330,7 @@
         <v>0</v>
       </c>
       <c r="E139" s="4" t="n">
-        <v>4002</v>
+        <v>4049</v>
       </c>
     </row>
     <row r="140">
@@ -3340,16 +3340,16 @@
         </is>
       </c>
       <c r="B140" s="4" t="n">
-        <v>2013</v>
+        <v>2002</v>
       </c>
       <c r="C140" s="4" t="n">
-        <v>2064</v>
+        <v>1995</v>
       </c>
       <c r="D140" s="4" t="n">
-        <v>1979</v>
+        <v>2077</v>
       </c>
       <c r="E140" s="4" t="n">
-        <v>2040</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="141">
@@ -3359,16 +3359,16 @@
         </is>
       </c>
       <c r="B141" s="4" t="n">
-        <v>1976</v>
+        <v>1978</v>
       </c>
       <c r="C141" s="4" t="n">
-        <v>2059</v>
+        <v>2039</v>
       </c>
       <c r="D141" s="4" t="n">
-        <v>2049</v>
+        <v>1941</v>
       </c>
       <c r="E141" s="4" t="n">
-        <v>2012</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="142">
@@ -3378,7 +3378,7 @@
         </is>
       </c>
       <c r="B142" s="4" t="n">
-        <v>4045</v>
+        <v>4035</v>
       </c>
       <c r="C142" s="4" t="n">
         <v>0</v>
@@ -3387,7 +3387,7 @@
         <v>0</v>
       </c>
       <c r="E142" s="4" t="n">
-        <v>4051</v>
+        <v>4061</v>
       </c>
     </row>
     <row r="143">
@@ -3397,16 +3397,16 @@
         </is>
       </c>
       <c r="B143" s="4" t="n">
-        <v>1998</v>
+        <v>2071</v>
       </c>
       <c r="C143" s="4" t="n">
-        <v>1985</v>
+        <v>1940</v>
       </c>
       <c r="D143" s="4" t="n">
-        <v>2070</v>
+        <v>2072</v>
       </c>
       <c r="E143" s="4" t="n">
-        <v>2043</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="144">
@@ -3416,16 +3416,16 @@
         </is>
       </c>
       <c r="B144" s="4" t="n">
-        <v>1976</v>
+        <v>2010</v>
       </c>
       <c r="C144" s="4" t="n">
-        <v>2009</v>
+        <v>2060</v>
       </c>
       <c r="D144" s="4" t="n">
-        <v>2041</v>
+        <v>2032</v>
       </c>
       <c r="E144" s="4" t="n">
-        <v>2070</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="145">
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="B145" s="4" t="n">
-        <v>3995</v>
+        <v>4071</v>
       </c>
       <c r="C145" s="4" t="n">
         <v>0</v>
@@ -3444,7 +3444,7 @@
         <v>0</v>
       </c>
       <c r="E145" s="4" t="n">
-        <v>4101</v>
+        <v>4025</v>
       </c>
     </row>
     <row r="146">
@@ -3454,16 +3454,16 @@
         </is>
       </c>
       <c r="B146" s="4" t="n">
-        <v>2048</v>
+        <v>2091</v>
       </c>
       <c r="C146" s="4" t="n">
-        <v>2011</v>
+        <v>1948</v>
       </c>
       <c r="D146" s="4" t="n">
-        <v>2023</v>
+        <v>2010</v>
       </c>
       <c r="E146" s="4" t="n">
-        <v>2014</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="147">
@@ -3473,13 +3473,13 @@
         </is>
       </c>
       <c r="B147" s="4" t="n">
-        <v>4028</v>
+        <v>4074</v>
       </c>
       <c r="C147" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D147" s="4" t="n">
-        <v>4068</v>
+        <v>4022</v>
       </c>
       <c r="E147" s="4" t="n">
         <v>0</v>
@@ -3492,16 +3492,16 @@
         </is>
       </c>
       <c r="B148" s="4" t="n">
-        <v>1982</v>
+        <v>1977</v>
       </c>
       <c r="C148" s="4" t="n">
-        <v>2064</v>
+        <v>2095</v>
       </c>
       <c r="D148" s="4" t="n">
-        <v>2060</v>
+        <v>2006</v>
       </c>
       <c r="E148" s="4" t="n">
-        <v>1990</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="149">
@@ -3511,16 +3511,16 @@
         </is>
       </c>
       <c r="B149" s="4" t="n">
-        <v>2038</v>
+        <v>2029</v>
       </c>
       <c r="C149" s="4" t="n">
-        <v>1930</v>
+        <v>2075</v>
       </c>
       <c r="D149" s="4" t="n">
-        <v>2068</v>
+        <v>1993</v>
       </c>
       <c r="E149" s="4" t="n">
-        <v>2060</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="150">
@@ -3530,16 +3530,16 @@
         </is>
       </c>
       <c r="B150" s="4" t="n">
-        <v>2092</v>
+        <v>2076</v>
       </c>
       <c r="C150" s="4" t="n">
-        <v>1974</v>
+        <v>2026</v>
       </c>
       <c r="D150" s="4" t="n">
-        <v>1979</v>
+        <v>1940</v>
       </c>
       <c r="E150" s="4" t="n">
-        <v>2051</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="151">
@@ -3549,13 +3549,13 @@
         </is>
       </c>
       <c r="B151" s="4" t="n">
-        <v>4045</v>
+        <v>4038</v>
       </c>
       <c r="C151" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D151" s="4" t="n">
-        <v>4051</v>
+        <v>4058</v>
       </c>
       <c r="E151" s="4" t="n">
         <v>0</v>
@@ -3568,16 +3568,16 @@
         </is>
       </c>
       <c r="B152" s="4" t="n">
-        <v>2038</v>
+        <v>2133</v>
       </c>
       <c r="C152" s="4" t="n">
-        <v>2006</v>
+        <v>1991</v>
       </c>
       <c r="D152" s="4" t="n">
-        <v>1979</v>
+        <v>1996</v>
       </c>
       <c r="E152" s="4" t="n">
-        <v>2073</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="153">
@@ -3587,16 +3587,16 @@
         </is>
       </c>
       <c r="B153" s="4" t="n">
-        <v>2042</v>
+        <v>2072</v>
       </c>
       <c r="C153" s="4" t="n">
-        <v>2040</v>
+        <v>1968</v>
       </c>
       <c r="D153" s="4" t="n">
-        <v>2007</v>
+        <v>2034</v>
       </c>
       <c r="E153" s="4" t="n">
-        <v>2007</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="154">
@@ -3606,10 +3606,10 @@
         </is>
       </c>
       <c r="B154" s="4" t="n">
-        <v>4043</v>
+        <v>4060</v>
       </c>
       <c r="C154" s="4" t="n">
-        <v>4053</v>
+        <v>4036</v>
       </c>
       <c r="D154" s="4" t="n">
         <v>0</v>
@@ -3644,10 +3644,10 @@
         </is>
       </c>
       <c r="B156" s="4" t="n">
-        <v>3981</v>
+        <v>4062</v>
       </c>
       <c r="C156" s="4" t="n">
-        <v>4115</v>
+        <v>4034</v>
       </c>
       <c r="D156" s="4" t="n">
         <v>0</v>
@@ -3663,10 +3663,10 @@
         </is>
       </c>
       <c r="B157" s="4" t="n">
-        <v>4055</v>
+        <v>4035</v>
       </c>
       <c r="C157" s="4" t="n">
-        <v>4041</v>
+        <v>4061</v>
       </c>
       <c r="D157" s="4" t="n">
         <v>0</v>
@@ -3682,16 +3682,16 @@
         </is>
       </c>
       <c r="B158" s="4" t="n">
-        <v>2000</v>
+        <v>1988</v>
       </c>
       <c r="C158" s="4" t="n">
-        <v>2057</v>
+        <v>2020</v>
       </c>
       <c r="D158" s="4" t="n">
-        <v>2003</v>
+        <v>2040</v>
       </c>
       <c r="E158" s="4" t="n">
-        <v>2036</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="159">
@@ -3701,13 +3701,13 @@
         </is>
       </c>
       <c r="B159" s="4" t="n">
-        <v>4051</v>
+        <v>4038</v>
       </c>
       <c r="C159" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D159" s="4" t="n">
-        <v>4045</v>
+        <v>4058</v>
       </c>
       <c r="E159" s="4" t="n">
         <v>0</v>
@@ -3720,16 +3720,16 @@
         </is>
       </c>
       <c r="B160" s="4" t="n">
-        <v>2072</v>
+        <v>2054</v>
       </c>
       <c r="C160" s="4" t="n">
-        <v>2007</v>
+        <v>1961</v>
       </c>
       <c r="D160" s="4" t="n">
-        <v>2047</v>
+        <v>2036</v>
       </c>
       <c r="E160" s="4" t="n">
-        <v>1970</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="161">
@@ -3739,16 +3739,16 @@
         </is>
       </c>
       <c r="B161" s="4" t="n">
-        <v>2019</v>
+        <v>1975</v>
       </c>
       <c r="C161" s="4" t="n">
-        <v>2001</v>
+        <v>2057</v>
       </c>
       <c r="D161" s="4" t="n">
-        <v>2047</v>
+        <v>1993</v>
       </c>
       <c r="E161" s="4" t="n">
-        <v>2029</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="162">
@@ -3758,16 +3758,16 @@
         </is>
       </c>
       <c r="B162" s="4" t="n">
-        <v>2045</v>
+        <v>1939</v>
       </c>
       <c r="C162" s="4" t="n">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="D162" s="4" t="n">
-        <v>2001</v>
+        <v>2085</v>
       </c>
       <c r="E162" s="4" t="n">
-        <v>2027</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="163">
@@ -3777,16 +3777,16 @@
         </is>
       </c>
       <c r="B163" s="4" t="n">
-        <v>2055</v>
+        <v>1997</v>
       </c>
       <c r="C163" s="4" t="n">
-        <v>1999</v>
+        <v>2095</v>
       </c>
       <c r="D163" s="4" t="n">
-        <v>2043</v>
+        <v>2032</v>
       </c>
       <c r="E163" s="4" t="n">
-        <v>1999</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="164">
@@ -3796,7 +3796,7 @@
         </is>
       </c>
       <c r="B164" s="4" t="n">
-        <v>4038</v>
+        <v>4078</v>
       </c>
       <c r="C164" s="4" t="n">
         <v>0</v>
@@ -3805,7 +3805,7 @@
         <v>0</v>
       </c>
       <c r="E164" s="4" t="n">
-        <v>4058</v>
+        <v>4018</v>
       </c>
     </row>
     <row r="165">
@@ -3815,16 +3815,16 @@
         </is>
       </c>
       <c r="B165" s="4" t="n">
-        <v>2031</v>
+        <v>2049</v>
       </c>
       <c r="C165" s="4" t="n">
-        <v>2015</v>
+        <v>1999</v>
       </c>
       <c r="D165" s="4" t="n">
-        <v>2048</v>
+        <v>1989</v>
       </c>
       <c r="E165" s="4" t="n">
-        <v>2002</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="166">
@@ -3837,10 +3837,10 @@
         <v>0</v>
       </c>
       <c r="C166" s="4" t="n">
-        <v>4064</v>
+        <v>4063</v>
       </c>
       <c r="D166" s="4" t="n">
-        <v>4032</v>
+        <v>4033</v>
       </c>
       <c r="E166" s="4" t="n">
         <v>0</v>
@@ -3853,16 +3853,16 @@
         </is>
       </c>
       <c r="B167" s="4" t="n">
-        <v>1959</v>
+        <v>2033</v>
       </c>
       <c r="C167" s="4" t="n">
-        <v>2014</v>
+        <v>1936</v>
       </c>
       <c r="D167" s="4" t="n">
-        <v>2024</v>
+        <v>2068</v>
       </c>
       <c r="E167" s="4" t="n">
-        <v>2099</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="168">
@@ -3872,16 +3872,16 @@
         </is>
       </c>
       <c r="B168" s="4" t="n">
-        <v>2020</v>
+        <v>2011</v>
       </c>
       <c r="C168" s="4" t="n">
-        <v>2046</v>
+        <v>2023</v>
       </c>
       <c r="D168" s="4" t="n">
-        <v>2009</v>
+        <v>2116</v>
       </c>
       <c r="E168" s="4" t="n">
-        <v>2021</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="169">
@@ -3894,10 +3894,10 @@
         <v>0</v>
       </c>
       <c r="C169" s="4" t="n">
-        <v>4086</v>
+        <v>4028</v>
       </c>
       <c r="D169" s="4" t="n">
-        <v>4010</v>
+        <v>4068</v>
       </c>
       <c r="E169" s="4" t="n">
         <v>0</v>
@@ -3910,16 +3910,16 @@
         </is>
       </c>
       <c r="B170" s="4" t="n">
-        <v>2088</v>
+        <v>2029</v>
       </c>
       <c r="C170" s="4" t="n">
-        <v>2026</v>
+        <v>2045</v>
       </c>
       <c r="D170" s="4" t="n">
-        <v>1935</v>
+        <v>2028</v>
       </c>
       <c r="E170" s="4" t="n">
-        <v>2047</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="171">
@@ -3929,7 +3929,7 @@
         </is>
       </c>
       <c r="B171" s="4" t="n">
-        <v>4068</v>
+        <v>4048</v>
       </c>
       <c r="C171" s="4" t="n">
         <v>0</v>
@@ -3938,7 +3938,7 @@
         <v>0</v>
       </c>
       <c r="E171" s="4" t="n">
-        <v>4028</v>
+        <v>4048</v>
       </c>
     </row>
     <row r="172">
@@ -3948,16 +3948,16 @@
         </is>
       </c>
       <c r="B172" s="4" t="n">
-        <v>2013</v>
+        <v>2058</v>
       </c>
       <c r="C172" s="4" t="n">
+        <v>2012</v>
+      </c>
+      <c r="D172" s="4" t="n">
+        <v>2030</v>
+      </c>
+      <c r="E172" s="4" t="n">
         <v>1996</v>
-      </c>
-      <c r="D172" s="4" t="n">
-        <v>2077</v>
-      </c>
-      <c r="E172" s="4" t="n">
-        <v>2010</v>
       </c>
     </row>
     <row r="173">
@@ -3967,16 +3967,16 @@
         </is>
       </c>
       <c r="B173" s="4" t="n">
-        <v>2045</v>
+        <v>2011</v>
       </c>
       <c r="C173" s="4" t="n">
-        <v>1984</v>
+        <v>1991</v>
       </c>
       <c r="D173" s="4" t="n">
-        <v>1972</v>
+        <v>2073</v>
       </c>
       <c r="E173" s="4" t="n">
-        <v>2095</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="174">
@@ -3986,16 +3986,16 @@
         </is>
       </c>
       <c r="B174" s="4" t="n">
-        <v>2011</v>
+        <v>2106</v>
       </c>
       <c r="C174" s="4" t="n">
-        <v>2039</v>
+        <v>2037</v>
       </c>
       <c r="D174" s="4" t="n">
-        <v>2105</v>
+        <v>1973</v>
       </c>
       <c r="E174" s="4" t="n">
-        <v>1941</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="175">
@@ -4005,16 +4005,16 @@
         </is>
       </c>
       <c r="B175" s="4" t="n">
-        <v>1954</v>
+        <v>2042</v>
       </c>
       <c r="C175" s="4" t="n">
-        <v>2095</v>
+        <v>2054</v>
       </c>
       <c r="D175" s="4" t="n">
-        <v>2051</v>
+        <v>1965</v>
       </c>
       <c r="E175" s="4" t="n">
-        <v>1996</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="176">
@@ -4024,7 +4024,7 @@
         </is>
       </c>
       <c r="B176" s="4" t="n">
-        <v>4008</v>
+        <v>3980</v>
       </c>
       <c r="C176" s="4" t="n">
         <v>0</v>
@@ -4033,7 +4033,7 @@
         <v>0</v>
       </c>
       <c r="E176" s="4" t="n">
-        <v>4088</v>
+        <v>4116</v>
       </c>
     </row>
     <row r="177">
@@ -4043,16 +4043,16 @@
         </is>
       </c>
       <c r="B177" s="4" t="n">
-        <v>1979</v>
+        <v>1983</v>
       </c>
       <c r="C177" s="4" t="n">
-        <v>2067</v>
+        <v>2038</v>
       </c>
       <c r="D177" s="4" t="n">
-        <v>1989</v>
+        <v>2061</v>
       </c>
       <c r="E177" s="4" t="n">
-        <v>2061</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="178">
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="B178" s="4" t="n">
-        <v>4033</v>
+        <v>4088</v>
       </c>
       <c r="C178" s="4" t="n">
         <v>0</v>
@@ -4071,7 +4071,7 @@
         <v>0</v>
       </c>
       <c r="E178" s="4" t="n">
-        <v>4063</v>
+        <v>4008</v>
       </c>
     </row>
     <row r="179">
@@ -4081,16 +4081,16 @@
         </is>
       </c>
       <c r="B179" s="4" t="n">
-        <v>2057</v>
+        <v>2078</v>
       </c>
       <c r="C179" s="4" t="n">
-        <v>2009</v>
+        <v>2013</v>
       </c>
       <c r="D179" s="4" t="n">
-        <v>2041</v>
+        <v>2013</v>
       </c>
       <c r="E179" s="4" t="n">
-        <v>1989</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="180">
@@ -4100,16 +4100,16 @@
         </is>
       </c>
       <c r="B180" s="4" t="n">
-        <v>2011</v>
+        <v>2029</v>
       </c>
       <c r="C180" s="4" t="n">
-        <v>2048</v>
+        <v>1988</v>
       </c>
       <c r="D180" s="4" t="n">
-        <v>1996</v>
+        <v>2047</v>
       </c>
       <c r="E180" s="4" t="n">
-        <v>2041</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="181">
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="B181" s="4" t="n">
-        <v>4102</v>
+        <v>3975</v>
       </c>
       <c r="C181" s="4" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
         <v>0</v>
       </c>
       <c r="E181" s="4" t="n">
-        <v>3994</v>
+        <v>4121</v>
       </c>
     </row>
     <row r="182">
@@ -4138,16 +4138,16 @@
         </is>
       </c>
       <c r="B182" s="4" t="n">
-        <v>2032</v>
+        <v>2054</v>
       </c>
       <c r="C182" s="4" t="n">
-        <v>1975</v>
+        <v>2004</v>
       </c>
       <c r="D182" s="4" t="n">
-        <v>2079</v>
+        <v>1984</v>
       </c>
       <c r="E182" s="4" t="n">
-        <v>2010</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="183">
@@ -4157,16 +4157,16 @@
         </is>
       </c>
       <c r="B183" s="4" t="n">
-        <v>2042</v>
+        <v>2037</v>
       </c>
       <c r="C183" s="4" t="n">
-        <v>2037</v>
+        <v>2054</v>
       </c>
       <c r="D183" s="4" t="n">
-        <v>1957</v>
+        <v>1985</v>
       </c>
       <c r="E183" s="4" t="n">
-        <v>2060</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="184">
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="B184" s="4" t="n">
-        <v>4011</v>
+        <v>3986</v>
       </c>
       <c r="C184" s="4" t="n">
         <v>0</v>
@@ -4185,7 +4185,7 @@
         <v>0</v>
       </c>
       <c r="E184" s="4" t="n">
-        <v>4085</v>
+        <v>4110</v>
       </c>
     </row>
     <row r="185">
@@ -4195,16 +4195,16 @@
         </is>
       </c>
       <c r="B185" s="4" t="n">
-        <v>2034</v>
+        <v>2008</v>
       </c>
       <c r="C185" s="4" t="n">
-        <v>1989</v>
+        <v>2066</v>
       </c>
       <c r="D185" s="4" t="n">
-        <v>2025</v>
+        <v>2036</v>
       </c>
       <c r="E185" s="4" t="n">
-        <v>2048</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="186">
@@ -4214,16 +4214,16 @@
         </is>
       </c>
       <c r="B186" s="4" t="n">
-        <v>1972</v>
+        <v>2049</v>
       </c>
       <c r="C186" s="4" t="n">
-        <v>2001</v>
+        <v>2012</v>
       </c>
       <c r="D186" s="4" t="n">
-        <v>2069</v>
+        <v>2032</v>
       </c>
       <c r="E186" s="4" t="n">
-        <v>2054</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="187">
@@ -4233,7 +4233,7 @@
         </is>
       </c>
       <c r="B187" s="4" t="n">
-        <v>4094</v>
+        <v>4097</v>
       </c>
       <c r="C187" s="4" t="n">
         <v>0</v>
@@ -4242,7 +4242,7 @@
         <v>0</v>
       </c>
       <c r="E187" s="4" t="n">
-        <v>4002</v>
+        <v>3999</v>
       </c>
     </row>
     <row r="188">
@@ -4252,16 +4252,16 @@
         </is>
       </c>
       <c r="B188" s="4" t="n">
-        <v>2019</v>
+        <v>1990</v>
       </c>
       <c r="C188" s="4" t="n">
-        <v>1973</v>
+        <v>2029</v>
       </c>
       <c r="D188" s="4" t="n">
+        <v>2046</v>
+      </c>
+      <c r="E188" s="4" t="n">
         <v>2031</v>
-      </c>
-      <c r="E188" s="4" t="n">
-        <v>2073</v>
       </c>
     </row>
     <row r="189">
@@ -4271,16 +4271,16 @@
         </is>
       </c>
       <c r="B189" s="4" t="n">
-        <v>2068</v>
+        <v>1997</v>
       </c>
       <c r="C189" s="4" t="n">
-        <v>2048</v>
+        <v>2000</v>
       </c>
       <c r="D189" s="4" t="n">
-        <v>1926</v>
+        <v>2113</v>
       </c>
       <c r="E189" s="4" t="n">
-        <v>2054</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="190">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="B190" s="4" t="n">
-        <v>4087</v>
+        <v>4059</v>
       </c>
       <c r="C190" s="4" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
         <v>0</v>
       </c>
       <c r="E190" s="4" t="n">
-        <v>4009</v>
+        <v>4037</v>
       </c>
     </row>
     <row r="191">
@@ -4309,16 +4309,16 @@
         </is>
       </c>
       <c r="B191" s="4" t="n">
-        <v>2057</v>
+        <v>2028</v>
       </c>
       <c r="C191" s="4" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D191" s="4" t="n">
-        <v>2012</v>
+        <v>2031</v>
       </c>
       <c r="E191" s="4" t="n">
-        <v>2003</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="192">
@@ -4328,16 +4328,16 @@
         </is>
       </c>
       <c r="B192" s="4" t="n">
-        <v>2035</v>
+        <v>1960</v>
       </c>
       <c r="C192" s="4" t="n">
-        <v>2090</v>
+        <v>2003</v>
       </c>
       <c r="D192" s="4" t="n">
-        <v>2032</v>
+        <v>2082</v>
       </c>
       <c r="E192" s="4" t="n">
-        <v>1939</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="193">
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="B193" s="4" t="n">
-        <v>4020</v>
+        <v>4090</v>
       </c>
       <c r="C193" s="4" t="n">
         <v>0</v>
@@ -4356,7 +4356,7 @@
         <v>0</v>
       </c>
       <c r="E193" s="4" t="n">
-        <v>4076</v>
+        <v>4006</v>
       </c>
     </row>
     <row r="194">
@@ -4385,10 +4385,10 @@
         </is>
       </c>
       <c r="B195" s="4" t="n">
-        <v>4078</v>
+        <v>4080</v>
       </c>
       <c r="C195" s="4" t="n">
-        <v>4018</v>
+        <v>4016</v>
       </c>
       <c r="D195" s="4" t="n">
         <v>0</v>
@@ -4404,10 +4404,10 @@
         </is>
       </c>
       <c r="B196" s="4" t="n">
-        <v>4011</v>
+        <v>4123</v>
       </c>
       <c r="C196" s="4" t="n">
-        <v>4085</v>
+        <v>3973</v>
       </c>
       <c r="D196" s="4" t="n">
         <v>0</v>
@@ -4442,13 +4442,13 @@
         </is>
       </c>
       <c r="B198" s="4" t="n">
-        <v>4040</v>
+        <v>4098</v>
       </c>
       <c r="C198" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D198" s="4" t="n">
-        <v>4056</v>
+        <v>3998</v>
       </c>
       <c r="E198" s="4" t="n">
         <v>0</v>
@@ -4461,16 +4461,16 @@
         </is>
       </c>
       <c r="B199" s="4" t="n">
-        <v>2004</v>
+        <v>1972</v>
       </c>
       <c r="C199" s="4" t="n">
-        <v>2029</v>
+        <v>2009</v>
       </c>
       <c r="D199" s="4" t="n">
-        <v>2059</v>
+        <v>2042</v>
       </c>
       <c r="E199" s="4" t="n">
-        <v>2004</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="200">
@@ -4480,16 +4480,16 @@
         </is>
       </c>
       <c r="B200" s="4" t="n">
-        <v>1988</v>
+        <v>2082</v>
       </c>
       <c r="C200" s="4" t="n">
-        <v>2054</v>
+        <v>1959</v>
       </c>
       <c r="D200" s="4" t="n">
-        <v>2011</v>
+        <v>2071</v>
       </c>
       <c r="E200" s="4" t="n">
-        <v>2043</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="201">
@@ -4499,13 +4499,13 @@
         </is>
       </c>
       <c r="B201" s="4" t="n">
-        <v>4038</v>
+        <v>4007</v>
       </c>
       <c r="C201" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D201" s="4" t="n">
-        <v>4058</v>
+        <v>4089</v>
       </c>
       <c r="E201" s="4" t="n">
         <v>0</v>
@@ -4518,13 +4518,13 @@
         </is>
       </c>
       <c r="B202" s="4" t="n">
-        <v>3995</v>
+        <v>4002</v>
       </c>
       <c r="C202" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D202" s="4" t="n">
-        <v>4101</v>
+        <v>4094</v>
       </c>
       <c r="E202" s="4" t="n">
         <v>0</v>
@@ -4537,16 +4537,16 @@
         </is>
       </c>
       <c r="B203" s="4" t="n">
-        <v>2047</v>
+        <v>1983</v>
       </c>
       <c r="C203" s="4" t="n">
-        <v>1957</v>
+        <v>2010</v>
       </c>
       <c r="D203" s="4" t="n">
-        <v>2060</v>
+        <v>2105</v>
       </c>
       <c r="E203" s="4" t="n">
-        <v>2032</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="204">
@@ -4556,16 +4556,16 @@
         </is>
       </c>
       <c r="B204" s="4" t="n">
-        <v>1990</v>
+        <v>2047</v>
       </c>
       <c r="C204" s="4" t="n">
-        <v>2061</v>
+        <v>2069</v>
       </c>
       <c r="D204" s="4" t="n">
-        <v>2015</v>
+        <v>1970</v>
       </c>
       <c r="E204" s="4" t="n">
-        <v>2030</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="205">
@@ -4575,13 +4575,13 @@
         </is>
       </c>
       <c r="B205" s="4" t="n">
-        <v>4025</v>
+        <v>4010</v>
       </c>
       <c r="C205" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D205" s="4" t="n">
-        <v>4071</v>
+        <v>4086</v>
       </c>
       <c r="E205" s="4" t="n">
         <v>0</v>
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="B207" s="4" t="n">
-        <v>4057</v>
+        <v>4004</v>
       </c>
       <c r="C207" s="4" t="n">
-        <v>4039</v>
+        <v>4092</v>
       </c>
       <c r="D207" s="4" t="n">
         <v>0</v>
@@ -4632,10 +4632,10 @@
         </is>
       </c>
       <c r="B208" s="4" t="n">
-        <v>4100</v>
+        <v>4109</v>
       </c>
       <c r="C208" s="4" t="n">
-        <v>3996</v>
+        <v>3987</v>
       </c>
       <c r="D208" s="4" t="n">
         <v>0</v>
@@ -4670,10 +4670,10 @@
         </is>
       </c>
       <c r="B210" s="4" t="n">
-        <v>4163</v>
+        <v>4038</v>
       </c>
       <c r="C210" s="4" t="n">
-        <v>3933</v>
+        <v>4058</v>
       </c>
       <c r="D210" s="4" t="n">
         <v>0</v>
@@ -4708,10 +4708,10 @@
         </is>
       </c>
       <c r="B212" s="4" t="n">
-        <v>3972</v>
+        <v>4055</v>
       </c>
       <c r="C212" s="4" t="n">
-        <v>4124</v>
+        <v>4041</v>
       </c>
       <c r="D212" s="4" t="n">
         <v>0</v>
@@ -4727,10 +4727,10 @@
         </is>
       </c>
       <c r="B213" s="4" t="n">
-        <v>3968</v>
+        <v>4069</v>
       </c>
       <c r="C213" s="4" t="n">
-        <v>4128</v>
+        <v>4027</v>
       </c>
       <c r="D213" s="4" t="n">
         <v>0</v>
@@ -4746,16 +4746,16 @@
         </is>
       </c>
       <c r="B214" s="4" t="n">
-        <v>2051</v>
+        <v>2049</v>
       </c>
       <c r="C214" s="4" t="n">
-        <v>2011</v>
+        <v>2029</v>
       </c>
       <c r="D214" s="4" t="n">
-        <v>2011</v>
+        <v>1998</v>
       </c>
       <c r="E214" s="4" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="215">
@@ -4765,13 +4765,13 @@
         </is>
       </c>
       <c r="B215" s="4" t="n">
-        <v>4005</v>
+        <v>4105</v>
       </c>
       <c r="C215" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D215" s="4" t="n">
-        <v>4091</v>
+        <v>3991</v>
       </c>
       <c r="E215" s="4" t="n">
         <v>0</v>
@@ -4784,16 +4784,16 @@
         </is>
       </c>
       <c r="B216" s="4" t="n">
-        <v>2040</v>
+        <v>1952</v>
       </c>
       <c r="C216" s="4" t="n">
-        <v>2057</v>
+        <v>2079</v>
       </c>
       <c r="D216" s="4" t="n">
-        <v>1996</v>
+        <v>1979</v>
       </c>
       <c r="E216" s="4" t="n">
-        <v>2003</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="217">
@@ -4803,16 +4803,16 @@
         </is>
       </c>
       <c r="B217" s="4" t="n">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="C217" s="4" t="n">
-        <v>1957</v>
+        <v>2035</v>
       </c>
       <c r="D217" s="4" t="n">
-        <v>2040</v>
+        <v>2029</v>
       </c>
       <c r="E217" s="4" t="n">
-        <v>2050</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="218">
@@ -4822,16 +4822,16 @@
         </is>
       </c>
       <c r="B218" s="4" t="n">
-        <v>1999</v>
+        <v>2107</v>
       </c>
       <c r="C218" s="4" t="n">
-        <v>2108</v>
+        <v>1960</v>
       </c>
       <c r="D218" s="4" t="n">
-        <v>1970</v>
+        <v>2062</v>
       </c>
       <c r="E218" s="4" t="n">
-        <v>2019</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="219">
@@ -4841,13 +4841,13 @@
         </is>
       </c>
       <c r="B219" s="4" t="n">
-        <v>4128</v>
+        <v>4050</v>
       </c>
       <c r="C219" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D219" s="4" t="n">
-        <v>3968</v>
+        <v>4046</v>
       </c>
       <c r="E219" s="4" t="n">
         <v>0</v>
@@ -4860,16 +4860,16 @@
         </is>
       </c>
       <c r="B220" s="4" t="n">
-        <v>1987</v>
+        <v>2020</v>
       </c>
       <c r="C220" s="4" t="n">
-        <v>2030</v>
+        <v>2013</v>
       </c>
       <c r="D220" s="4" t="n">
-        <v>2042</v>
+        <v>2011</v>
       </c>
       <c r="E220" s="4" t="n">
-        <v>2037</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="221">
@@ -4879,16 +4879,16 @@
         </is>
       </c>
       <c r="B221" s="4" t="n">
-        <v>1961</v>
+        <v>2053</v>
       </c>
       <c r="C221" s="4" t="n">
-        <v>2027</v>
+        <v>1987</v>
       </c>
       <c r="D221" s="4" t="n">
-        <v>2055</v>
+        <v>1985</v>
       </c>
       <c r="E221" s="4" t="n">
-        <v>2053</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="222">
@@ -4898,10 +4898,10 @@
         </is>
       </c>
       <c r="B222" s="4" t="n">
-        <v>4055</v>
+        <v>4057</v>
       </c>
       <c r="C222" s="4" t="n">
-        <v>4041</v>
+        <v>4039</v>
       </c>
       <c r="D222" s="4" t="n">
         <v>0</v>
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="B224" s="4" t="n">
-        <v>4004</v>
+        <v>4067</v>
       </c>
       <c r="C224" s="4" t="n">
-        <v>4092</v>
+        <v>4029</v>
       </c>
       <c r="D224" s="4" t="n">
         <v>0</v>
@@ -4955,10 +4955,10 @@
         </is>
       </c>
       <c r="B225" s="4" t="n">
-        <v>4043</v>
+        <v>4046</v>
       </c>
       <c r="C225" s="4" t="n">
-        <v>4053</v>
+        <v>4050</v>
       </c>
       <c r="D225" s="4" t="n">
         <v>0</v>
@@ -4974,10 +4974,10 @@
         </is>
       </c>
       <c r="B226" s="4" t="n">
-        <v>4100</v>
+        <v>4071</v>
       </c>
       <c r="C226" s="4" t="n">
-        <v>3996</v>
+        <v>4025</v>
       </c>
       <c r="D226" s="4" t="n">
         <v>0</v>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="B227" s="4" t="n">
-        <v>3995</v>
+        <v>4004</v>
       </c>
       <c r="C227" s="4" t="n">
-        <v>4101</v>
+        <v>4092</v>
       </c>
       <c r="D227" s="4" t="n">
         <v>0</v>
@@ -5031,10 +5031,10 @@
         </is>
       </c>
       <c r="B229" s="4" t="n">
-        <v>4017</v>
+        <v>4099</v>
       </c>
       <c r="C229" s="4" t="n">
-        <v>4079</v>
+        <v>3997</v>
       </c>
       <c r="D229" s="4" t="n">
         <v>0</v>
@@ -5050,16 +5050,16 @@
         </is>
       </c>
       <c r="B230" s="4" t="n">
-        <v>1975</v>
+        <v>2031</v>
       </c>
       <c r="C230" s="4" t="n">
-        <v>2056</v>
+        <v>2067</v>
       </c>
       <c r="D230" s="4" t="n">
-        <v>2010</v>
+        <v>1974</v>
       </c>
       <c r="E230" s="4" t="n">
-        <v>2055</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="231">
@@ -5069,16 +5069,16 @@
         </is>
       </c>
       <c r="B231" s="4" t="n">
-        <v>2018</v>
+        <v>2098</v>
       </c>
       <c r="C231" s="4" t="n">
-        <v>1999</v>
+        <v>2003</v>
       </c>
       <c r="D231" s="4" t="n">
-        <v>2032</v>
+        <v>1943</v>
       </c>
       <c r="E231" s="4" t="n">
-        <v>2047</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="232">
@@ -5088,13 +5088,13 @@
         </is>
       </c>
       <c r="B232" s="4" t="n">
-        <v>4066</v>
+        <v>4114</v>
       </c>
       <c r="C232" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D232" s="4" t="n">
-        <v>4030</v>
+        <v>3982</v>
       </c>
       <c r="E232" s="4" t="n">
         <v>0</v>
@@ -5107,16 +5107,16 @@
         </is>
       </c>
       <c r="B233" s="4" t="n">
-        <v>2046</v>
+        <v>2055</v>
       </c>
       <c r="C233" s="4" t="n">
-        <v>2001</v>
+        <v>2018</v>
       </c>
       <c r="D233" s="4" t="n">
-        <v>1998</v>
+        <v>2021</v>
       </c>
       <c r="E233" s="4" t="n">
-        <v>2051</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="234">
@@ -5126,16 +5126,16 @@
         </is>
       </c>
       <c r="B234" s="4" t="n">
-        <v>2046</v>
+        <v>2021</v>
       </c>
       <c r="C234" s="4" t="n">
-        <v>2000</v>
+        <v>1975</v>
       </c>
       <c r="D234" s="4" t="n">
-        <v>2031</v>
+        <v>2018</v>
       </c>
       <c r="E234" s="4" t="n">
-        <v>2019</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="235">
@@ -5145,16 +5145,16 @@
         </is>
       </c>
       <c r="B235" s="4" t="n">
-        <v>2027</v>
+        <v>2078</v>
       </c>
       <c r="C235" s="4" t="n">
-        <v>1995</v>
+        <v>2045</v>
       </c>
       <c r="D235" s="4" t="n">
-        <v>2102</v>
+        <v>2018</v>
       </c>
       <c r="E235" s="4" t="n">
-        <v>1972</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="236">
@@ -5164,13 +5164,13 @@
         </is>
       </c>
       <c r="B236" s="4" t="n">
-        <v>4012</v>
+        <v>4061</v>
       </c>
       <c r="C236" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D236" s="4" t="n">
-        <v>4084</v>
+        <v>4035</v>
       </c>
       <c r="E236" s="4" t="n">
         <v>0</v>
@@ -5183,16 +5183,16 @@
         </is>
       </c>
       <c r="B237" s="4" t="n">
-        <v>2012</v>
+        <v>2062</v>
       </c>
       <c r="C237" s="4" t="n">
-        <v>2013</v>
+        <v>1966</v>
       </c>
       <c r="D237" s="4" t="n">
-        <v>2020</v>
+        <v>2073</v>
       </c>
       <c r="E237" s="4" t="n">
-        <v>2051</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="238">
@@ -5202,10 +5202,10 @@
         </is>
       </c>
       <c r="B238" s="4" t="n">
-        <v>4116</v>
+        <v>4123</v>
       </c>
       <c r="C238" s="4" t="n">
-        <v>3980</v>
+        <v>3973</v>
       </c>
       <c r="D238" s="4" t="n">
         <v>0</v>
@@ -5221,10 +5221,10 @@
         </is>
       </c>
       <c r="B239" s="4" t="n">
-        <v>4010</v>
+        <v>3970</v>
       </c>
       <c r="C239" s="4" t="n">
-        <v>4086</v>
+        <v>4126</v>
       </c>
       <c r="D239" s="4" t="n">
         <v>0</v>
@@ -5259,10 +5259,10 @@
         </is>
       </c>
       <c r="B241" s="4" t="n">
-        <v>4007</v>
+        <v>4078</v>
       </c>
       <c r="C241" s="4" t="n">
-        <v>4089</v>
+        <v>4018</v>
       </c>
       <c r="D241" s="4" t="n">
         <v>0</v>
@@ -5297,10 +5297,10 @@
         </is>
       </c>
       <c r="B243" s="4" t="n">
-        <v>4060</v>
+        <v>4056</v>
       </c>
       <c r="C243" s="4" t="n">
-        <v>4036</v>
+        <v>4040</v>
       </c>
       <c r="D243" s="4" t="n">
         <v>0</v>
@@ -5316,10 +5316,10 @@
         </is>
       </c>
       <c r="B244" s="4" t="n">
-        <v>4054</v>
+        <v>4058</v>
       </c>
       <c r="C244" s="4" t="n">
-        <v>4042</v>
+        <v>4038</v>
       </c>
       <c r="D244" s="4" t="n">
         <v>0</v>
@@ -5354,13 +5354,13 @@
         </is>
       </c>
       <c r="B246" s="4" t="n">
-        <v>4041</v>
+        <v>3978</v>
       </c>
       <c r="C246" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D246" s="4" t="n">
-        <v>4055</v>
+        <v>4118</v>
       </c>
       <c r="E246" s="4" t="n">
         <v>0</v>
@@ -5373,16 +5373,16 @@
         </is>
       </c>
       <c r="B247" s="4" t="n">
-        <v>1979</v>
+        <v>2031</v>
       </c>
       <c r="C247" s="4" t="n">
-        <v>2104</v>
+        <v>2039</v>
       </c>
       <c r="D247" s="4" t="n">
-        <v>2027</v>
+        <v>2024</v>
       </c>
       <c r="E247" s="4" t="n">
-        <v>1986</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="248">
@@ -5392,16 +5392,16 @@
         </is>
       </c>
       <c r="B248" s="4" t="n">
-        <v>1997</v>
+        <v>2080</v>
       </c>
       <c r="C248" s="4" t="n">
-        <v>2055</v>
+        <v>2028</v>
       </c>
       <c r="D248" s="4" t="n">
-        <v>1988</v>
+        <v>1967</v>
       </c>
       <c r="E248" s="4" t="n">
-        <v>2056</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="249">
@@ -5411,13 +5411,13 @@
         </is>
       </c>
       <c r="B249" s="4" t="n">
-        <v>4071</v>
+        <v>4106</v>
       </c>
       <c r="C249" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D249" s="4" t="n">
-        <v>4025</v>
+        <v>3990</v>
       </c>
       <c r="E249" s="4" t="n">
         <v>0</v>
@@ -5430,13 +5430,13 @@
         </is>
       </c>
       <c r="B250" s="4" t="n">
-        <v>4020</v>
+        <v>4094</v>
       </c>
       <c r="C250" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D250" s="4" t="n">
-        <v>4076</v>
+        <v>4002</v>
       </c>
       <c r="E250" s="4" t="n">
         <v>0</v>
@@ -5449,16 +5449,16 @@
         </is>
       </c>
       <c r="B251" s="4" t="n">
-        <v>2047</v>
+        <v>1973</v>
       </c>
       <c r="C251" s="4" t="n">
-        <v>2041</v>
+        <v>2061</v>
       </c>
       <c r="D251" s="4" t="n">
-        <v>2019</v>
+        <v>1964</v>
       </c>
       <c r="E251" s="4" t="n">
-        <v>1989</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="252">
@@ -5468,16 +5468,16 @@
         </is>
       </c>
       <c r="B252" s="4" t="n">
-        <v>1967</v>
+        <v>1963</v>
       </c>
       <c r="C252" s="4" t="n">
-        <v>2043</v>
+        <v>2030</v>
       </c>
       <c r="D252" s="4" t="n">
-        <v>1993</v>
+        <v>2037</v>
       </c>
       <c r="E252" s="4" t="n">
-        <v>2093</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="253">
@@ -5487,13 +5487,13 @@
         </is>
       </c>
       <c r="B253" s="4" t="n">
-        <v>4017</v>
+        <v>4024</v>
       </c>
       <c r="C253" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D253" s="4" t="n">
-        <v>4079</v>
+        <v>4072</v>
       </c>
       <c r="E253" s="4" t="n">
         <v>0</v>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="B255" s="4" t="n">
-        <v>4061</v>
+        <v>4009</v>
       </c>
       <c r="C255" s="4" t="n">
-        <v>4035</v>
+        <v>4087</v>
       </c>
       <c r="D255" s="4" t="n">
         <v>0</v>
@@ -5544,10 +5544,10 @@
         </is>
       </c>
       <c r="B256" s="4" t="n">
-        <v>4016</v>
+        <v>4078</v>
       </c>
       <c r="C256" s="4" t="n">
-        <v>4080</v>
+        <v>4018</v>
       </c>
       <c r="D256" s="4" t="n">
         <v>0</v>
